--- a/data/perguntas.xlsx
+++ b/data/perguntas.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="perguntas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="como_usar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="produtos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="como_usar" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,18 +28,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -50,7 +44,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3A34"/>
+        <fgColor rgb="001B131A"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,15 +60,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -441,17 +434,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +490,16 @@
           <t>explicacao_b</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>produtos</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>imagem_pergunta</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -502,22 +507,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Cliente tem raiz oleosa e pontas ressecadas. Como aplicar o condicionador?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Do comprimento às pontas, evitando a raiz</t>
+          <t>Progressiva alisante sem formol, com liso por até 4 meses</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Da raiz às pontas, para hidratar tudo igual</t>
+          <t>Neutralizar o pH ao final de uma química</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -527,12 +532,22 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>O condicionador tem ativos pesados que, na raiz, misturam-se à oleosidade natural e deixam o couro cabeludo com aspecto sujo mais rápido. As pontas são a parte mais velha e ressecada do fio, por isso precisam mais.</t>
+          <t>É a Não Chore Mais: progressiva sem formol e sem ácido glioxílico, sem ardência, com liso de até 4 meses.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Passar na raiz de quem já tem oleosidade tende a pesar o cabelo e acelerar o aspecto de sujo. A raiz produz óleo natural e não precisa de tanta hidratação quanto as pontas.</t>
+          <t>Neutralizar o pH é função do NeutraQuimic, usado ao final da química.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>nao-chore-mais</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>nao-chore-mais</t>
         </is>
       </c>
     </row>
@@ -542,37 +557,47 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Com que frequência quem tem cabelo oleoso deve lavar?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Só 1 vez por semana, para o couro 'aprender' a produzir menos óleo</t>
+          <t>Limpeza profunda antes de um procedimento químico</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sempre que sentir necessidade, com shampoo suave</t>
+          <t>Shampoo de uso diário para manter a química</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Espaçar demais acumula oleosidade, suor e resíduos, podendo causar coceira e caspa. Não há evidência de que o couro 'aprende' a produzir menos óleo.</t>
+          <t>É o Shampoo Anti Resíduo: remove sujidade e resíduos e prepara os fios para progressivas e selagens.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Lavar quando o couro cabeludo pede mantém a pele limpa e equilibrada. Shampoos suaves permitem lavagens frequentes sem agredir.</t>
+          <t>Manutenção diária pós-química é função do Day Use, não do Anti Resíduo, que é indicado antes das químicas.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>shampoo-anti-residuo</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>shampoo-anti-residuo</t>
         </is>
       </c>
     </row>
@@ -582,37 +607,47 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>O cabelo estica como chiclete e não volta ao normal. Qual tratamento indicar?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Reconstrução (reposição de proteínas)</t>
+          <t>Reconstrutor de 5 minutos para cabelo emborrachado</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hidratação com máscara de água e umectantes</t>
+          <t>Alisante orgânico de passo único com 12 óleos</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Fio elástico e que quebra ao esticar perdeu massa proteica (queratina). A reconstrução repõe essa estrutura. Depois, hidratar e nutrir para equilibrar.</t>
+          <t>Reconstruir cabelo emborrachado em 5 minutos é o SOS Extreme.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>A hidratação repõe água, mas o problema aqui é falta de estrutura. Só hidratar não devolve resistência ao fio danificado.</t>
+          <t>É a Perfecta Bio Definitive: alinha e disciplina em um só passo, com 19 aminoácidos e 12 óleos nobres.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>perfecta</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>perfecta</t>
         </is>
       </c>
     </row>
@@ -622,37 +657,47 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Para que serve o shampoo antirresíduos (ou de limpeza profunda)?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Ser usado em toda lavagem como shampoo comum</t>
+          <t>Selagem semi definitiva com brilho gloss, por até 3 meses</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Remover acúmulo de produtos, silicone e poluição, em uso ocasional</t>
+          <t>Fluído que facilita a escova e acelera a secagem</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Por ser mais potente, o uso diário pode ressecar fios e couro cabeludo. Ele é um complemento, não o shampoo do dia a dia.</t>
+          <t>É a Selagem 3D Gloss Sealant, com BioComplex (ácido hialurônico, 19 aminoácidos, queratina, seda e macadâmia).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Ele é mais forte e remove o acúmulo. Costuma ser usado a cada 15 dias ou conforme o rótulo, antes de tratamentos para melhorar a absorção.</t>
+          <t>Facilitar a escova e secar mais rápido é função do Brush 9x1.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>selagem-3d</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>selagem-3d</t>
         </is>
       </c>
     </row>
@@ -662,37 +707,47 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>A cliente quer deixar a máscara de hidratação por horas ou dormir com ela. Vale a pena?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Não, respeitar o tempo do rótulo, pois mais tempo não potencializa o efeito</t>
+          <t>Spray com perfume e proteção térmica</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sim, quanto mais tempo agindo, mais hidratação</t>
+          <t>Botox capilar que alinha e repõe massa</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>As máscaras são formuladas para agir no tempo indicado. Passado isso, o fio já absorveu o que podia.</t>
+          <t>Perfume com proteção térmica é o Shield.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Exceder o tempo pode até causar excesso de umidade no fio e couro cabeludo, sem ganho de resultado. Algumas linhas específicas permitem, mas só se o rótulo disser.</t>
+          <t>É o Boratx 19 Amino: alinha, hidrata, repõe massa e sela cutículas, sem formol e sem ácido glioxílico.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>boratx</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>boratx</t>
         </is>
       </c>
     </row>
@@ -702,37 +757,47 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Cliente com cabelo colorido ou com química quer manter o resultado. O que sugerir?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Shampoo antirresíduos toda lavagem para deixar limpo</t>
+          <t>Tratamento termoativado de alinhamento e nutrição</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Linha própria para cabelos coloridos/quimicamente tratados</t>
+          <t>Leave-in para engrossar fios finos</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Shampoos de limpeza profunda removem mais rápido a cor e os produtos de tratamento, encurtando a duração do resultado.</t>
+          <t>É o Perfeitox: com 19 aminoácidos e 12 óleos, é potencializado pelo calor do secador e da prancha.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Essas linhas são mais suaves e ajudam a prolongar cor e alinhamento, além de repor o que a química retira.</t>
+          <t>Engrossar fios finos é função do Leave-in Volumize.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>perfeitox</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>perfeitox</t>
         </is>
       </c>
     </row>
@@ -742,22 +807,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>A cliente tem descamação e coceira no couro cabeludo. O que recomendar?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Shampoo anticaspa e deixar agir alguns minutos antes de enxaguar</t>
+          <t>Neutralizar o pH e eliminar o cheiro após a química</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Passar óleo no couro cabeludo para hidratar a caspa</t>
+          <t>Dar brilho espelhado com cauterização</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -767,12 +832,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Ativos anticaspa precisam de contato com a pele para agir, por isso o tempo de pausa indicado no rótulo faz diferença.</t>
+          <t>É o NeutraQuimic: equilibra o pH, religa as pontes de dissulfeto e elimina o mau cheiro do cabelo molhado.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Óleos podem alimentar fungos que causam a caspa (como a Malassezia) e piorar o quadro em muitos casos.</t>
+          <t>Brilho espelhado com cauterização é função do CauterGloss.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>neutraquimic</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>neutraquimic</t>
         </is>
       </c>
     </row>
@@ -782,22 +857,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Cliente pergunta se um tônico capilar vai resolver a queda de cabelo dela. Qual a resposta mais honesta?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Sim, o tônico resolve qualquer tipo de queda</t>
+          <t>Limpeza profunda antes da química</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Cosméticos ajudam a cuidar do fio, mas queda intensa deve ser avaliada por dermatologista</t>
+          <t>Cauterização que sela cutículas e pode ser usada por gestantes e crianças</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +882,22 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Nenhum cosmético substitui diagnóstico médico. Garantir resultado gera frustração e problemas com reclamações.</t>
+          <t>Limpeza profunda pré-química é do Shampoo Anti Resíduo.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Queda pode ter causas como estresse, anemia, hormônios ou tireoide, que precisam de diagnóstico. Prometer cura pode atrasar o tratamento.</t>
+          <t>É o CauterGloss: pH 4,5, livre de ativos agressivos, indicado para todos os cabelos e liberado para gestantes, lactantes e crianças.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>cautergloss</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>cautergloss</t>
         </is>
       </c>
     </row>
@@ -822,22 +907,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Quando aplicar o protetor térmico?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Antes de secador, chapinha ou babyliss</t>
+          <t>Reconstrutor anti-emborrachamento de ação em 5 minutos</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Depois de usar o calor, para reparar</t>
+          <t>Óleo finalizador com 12 óleos nobres</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -847,12 +932,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Ele forma uma barreira que reduz o dano da alta temperatura, por isso precisa estar no fio antes de o calor chegar.</t>
+          <t>É o SOS Extreme: reconstrutor para cabelos muito fragilizados, com sericina, D-pantenol, nanoqueratina e elixir de 12 óleos.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Aplicado depois, o dano já aconteceu e o produto não desfaz. A função dele é proteger, não reparar.</t>
+          <t>O óleo com 12 óleos nobres é o Elixir 12 Oils, um finalizador.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>sos-extreme</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>sos-extreme</t>
         </is>
       </c>
     </row>
@@ -862,37 +957,47 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Qual temperatura de água é melhor para lavar os cabelos?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bem quente, pois limpa melhor</t>
+          <t>Shampoo + máscara de cronograma capilar em passo único</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Morna, evitando água muito quente</t>
+          <t>Kit para tratar o couro cabeludo</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Água muito quente ressecá o fio, pode irritar o couro cabeludo e ainda estimular mais oleosidade.</t>
+          <t>É o Pra Tudo 25 Ativos: shampoo e máscara que hidratam, nutrem e reconstroem com um só produto.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Água morna limpa bem sem retirar em excesso a proteção natural do couro cabeludo e do fio.</t>
+          <t>Tratar o couro cabeludo é o kit Scalp Repair.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>pra-tudo</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>pra-tudo</t>
         </is>
       </c>
     </row>
@@ -902,22 +1007,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Onde aplicar o leave-in?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Nos fios úmidos, do comprimento às pontas</t>
+          <t>Kit diário de shampoo e máscara para manter a química</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Direto no couro cabeludo</t>
+          <t>Progressiva de passo único</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -927,12 +1032,22 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Leave-in não é enxaguado, então aplicado no comprimento ele protege e facilita o pentear sem pesar na raiz.</t>
+          <t>É o Day Use Pós-Química: shampoo e máscara que prolongam o resultado de progressivas, colorações e descolorações.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>No couro cabeludo pode acumular, entupir poros e deixar a raiz pesada ou oleosa.</t>
+          <t>Alisar em passo único é função da Perfecta, não do Day Use.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>day-use-pos-quimica</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>day-use-pos-quimica</t>
         </is>
       </c>
     </row>
@@ -942,37 +1057,47 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Cliente com cabelo fino quer usar óleo capilar. Como orientar?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Bastante óleo, da raiz às pontas</t>
+          <t>Linha de 3 passos para nutrir, com óleos preciosos</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Poucas gotas, só nas pontas</t>
+          <t>Linha de 3 passos para reconstruir com queratina</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Excesso de óleo deixa o cabelo fino achatado e com aspecto sujo, principalmente na raiz.</t>
+          <t>É o Day Use Super Nutrição: shampoo, condicionador e máscara com óleos como macadâmia e coco, indicados a cabelos porosos e com frizz.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Fios finos pesam facilmente. Uma quantidade pequena nas pontas dá brilho e controle sem perder volume.</t>
+          <t>Reconstruir com queratina é o Day Use Super Reparação.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>day-use-nutricao</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>day-use-nutricao</t>
         </is>
       </c>
     </row>
@@ -982,22 +1107,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Qual a melhor forma de pentear cabelo cacheado?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Úmido, com condicionador ou leave-in e pente de dentes largos</t>
+          <t>Linha de 3 passos para hidratar, com pantenol e ácido hialurônico</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Seco, com escova de cerdas finas</t>
+          <t>Linha de 3 passos para nutrir com óleos</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1007,12 +1132,22 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>O produto e a água dão deslizamento, diminuindo quebra e frizz, e preservam a definição dos cachos.</t>
+          <t>É o Day Use Super Hidratação, indicado a cabelos ressecados, danificados e opacos.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Pentear seco quebra fios e desfaz os cachos, deixando o volume desorganizado.</t>
+          <t>Nutrir com óleos é o Day Use Super Nutrição.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>day-use-hidratacao</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>day-use-hidratacao</t>
         </is>
       </c>
     </row>
@@ -1022,22 +1157,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Cliente com cabelo loiro amarelado pergunta sobre shampoo matizador. O que responder?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Ele clareia o cabelo, então pode usar todos os dias</t>
+          <t>Linha de 3 passos para hidratar</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Ele neutraliza tons amarelados, usar 1 a 2 vezes por semana ou conforme o rótulo</t>
+          <t>Linha de 3 passos para reparar e fortalecer, com queratina</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1047,12 +1182,22 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Matizador não tem poder de clareamento. Usar sempre pode acumular pigmento e ressecar.</t>
+          <t>Hidratar com pantenol e ácido hialurônico é o Day Use Super Hidratação.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>O pigmento violeta neutraliza o amarelo. Não clareia, só ajusta o tom, e o excesso pode deixar o cabelo acinzentado ou arroxeado.</t>
+          <t>É o Day Use Super Reparação: queratina, proteína da seda e da soja contra a quebra.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>day-use-reparacao</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>day-use-reparacao</t>
         </is>
       </c>
     </row>
@@ -1062,22 +1207,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Shampoo e condicionador precisam ser sempre da mesma linha para funcionar?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Não, dá para combinar linhas conforme a necessidade do cabelo</t>
+          <t>Tratar queda e irritação do couro cabeludo após química</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sim, senão o produto perde o efeito</t>
+          <t>Engrossar fios finos</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1087,12 +1232,22 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Muitas pessoas usam shampoo e condicionador de linhas diferentes. O importante é atender à necessidade do fio (oleosidade, ressecamento, etc.).</t>
+          <t>É o Scalp Repair: restaura o pH do couro, reduz a inflamação e fortalece folículos.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Linhas combinadas funcionam bem. Manter a mesma linha é uma escolha de praticidade, não uma regra técnica.</t>
+          <t>Engrossar fios finos é função do Leave-in Volumize.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>scalp-repair</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>scalp-repair</t>
         </is>
       </c>
     </row>
@@ -1102,37 +1257,47 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Produtos</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>O que significa o símbolo do potinho aberto com um número na embalagem (ex.: 12M)?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Data de fabricação do produto</t>
+          <t>Leave-in que engrossa fios finos e afinados</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Tempo em meses que o produto pode ser usado após aberto</t>
+          <t>Tratar queda e irritação do couro cabeludo</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>A data de fabricação vem impressa separadamente. O potinho é sobre o tempo de uso depois de aberto.</t>
+          <t>É o Volumize: aumenta o calibre do fio, dá densidade e protege do calor.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Esse símbolo (PAO) informa por quanto tempo o produto aberto mantém qualidade e segurança. A validade geral fica no rótulo, em outro campo.</t>
+          <t>Tratar o couro cabeludo é o Scalp Repair.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>volumize</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>volumize</t>
         </is>
       </c>
     </row>
@@ -1142,37 +1307,47 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Atendimento</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>O cliente recebeu um frasco quebrado ou vazando. Como agir?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Pedir número do pedido e fotos do produto e da embalagem para abrir troca ou reembolso</t>
+          <t>Fluído 9 em 1 que acelera a secagem</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Pedir que aguarde 30 dias para ver se o problema se resolve</t>
+          <t>Óleo finalizador com 12 óleos nobres</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Fotos e número do pedido documentam a avaria e agilizam o processo com a transportadora.</t>
+          <t>Acelerar a secagem é o Brush 9x1.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Esperar não resolve o problema e pode extrapolar prazos de reclamação.</t>
+          <t>É o Elixir 12 Oils: nutrição sem peso, antifrizz e brilho.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>elixir-12-oils</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>elixir-12-oils</t>
         </is>
       </c>
     </row>
@@ -1182,22 +1357,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Atendimento</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Em compras online no Brasil, em quanto tempo o cliente pode desistir sem justificativa?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Até 30 dias após a compra</t>
+          <t>Queratina líquida em spray</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Até 7 dias após o recebimento</t>
+          <t>Óleo leve com ômegas 3, 6 e 9 que nutre sem pesar</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1207,12 +1382,22 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>O prazo legal é 7 dias, não 30. A loja pode oferecer prazo maior como política própria, mas não é obrigatório.</t>
+          <t>Queratina líquida em spray é o Biokeratin.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Pelo Código de Defesa do Consumidor (art. 49), o direito de arrependimento vale por 7 dias corridos a partir do recebimento em compras fora do estabelecimento.</t>
+          <t>É o Elixir Light, leve e multifuncional.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>elixir-light</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>elixir-light</t>
         </is>
       </c>
     </row>
@@ -1222,37 +1407,47 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Produtos</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Qual a diferença entre 'vegano' e 'cruelty free'?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Vegano: sem ingredientes de origem animal. Cruelty free: não testado em animais</t>
+          <t>Spray protetor térmico perfumado</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>São a mesma coisa</t>
+          <t>Reparar pontas com argan, macadâmia e linum</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Um produto pode ser cruelty free e conter, por exemplo, mel ou cera de abelha (não vegano), e um vegano pode ter sido testado em animais.</t>
+          <t>O spray perfumado com proteção térmica é o Shield.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>São conceitos diferentes. Um trata da composição, o outro dos testes realizados.</t>
+          <t>É o Óleo de Argan e Macadâmia, reparador de pontas.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>oleo-argan</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>oleo-argan</t>
         </is>
       </c>
     </row>
@@ -1262,37 +1457,47 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Atendimento</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Cliente relata coceira e vermelhidão após usar um produto novo. O que orientar?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Continuar usando para o couro cabeludo se acostumar</t>
+          <t>Fluído 9 em 1 que reduz até 30% o tempo de secagem</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Suspender o uso, enxaguar bem e procurar orientação médica se persistir</t>
+          <t>Óleo para umectação noturna</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Persistir pode piorar a irritação e causar lesões. 'Acostumar' não é um método seguro.</t>
+          <t>É o Brush 9x1: protege do calor e da cor, desembaraça e dá brilho 3D.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Sinais de reação indicam sensibilidade a algum ingrediente. Parar o uso evita agravamento, e é importante saber o lote/ingredientes para a avaliação.</t>
+          <t>Umectação noturna é uso de óleos como Elixir.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>brush</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>brush</t>
         </is>
       </c>
     </row>
@@ -1302,37 +1507,47 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Por que fazer teste de alergia antes de tintura e alisamentos?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Para identificar sensibilidade aos ingredientes antes de aplicar no couro cabeludo todo</t>
+          <t>Máscara de reconstrução</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Não é necessário, só para quem já teve reação</t>
+          <t>Perfume capilar com protetor térmico e desembaraçante</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Reações podem surgir mesmo sem histórico prévio. O teste (geralmente atrás da orelha ou dobra do braço) dá a chance de detectar o problema em pequena escala.</t>
+          <t>Reconstruir com máscara é função de produtos como SOS Extreme e Day Use.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Alergia pode aparecer a qualquer momento, mesmo em quem sempre usou. Pular o teste é o maior risco.</t>
+          <t>É o Shield: protege do calor, desembaraça cabelo seco ou molhado e perfuma.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>shield</t>
         </is>
       </c>
     </row>
@@ -1342,37 +1557,47 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Atendimento</t>
+          <t>Reconheça a embalagem</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>O rastreio do pedido não atualiza há 1 dia. O que responder?</t>
+          <t>Observe a embalagem. Qual é a função deste produto?</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Cancelar o pedido, pois com certeza foi extraviado</t>
+          <t>Queratina líquida bioidêntica em spray</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Pode levar até 24 a 48h para aparecer movimentação, e a equipe acompanha o caso</t>
+          <t>Leave-in para dar volume</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Cancelar sem apuração gera retrabalho e frustra o cliente que já esperava receber.</t>
+          <t>É o Biokeratin, queratina feita por engenharia genética para imitar a humana.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Atualizações dependem da leitura dos scans da transportadora, que às vezes atrasa. Se passar do prazo, aí sim abrir chamado.</t>
+          <t>Volume em fios finos é função do Volumize.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>biokeratin</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>biokeratin</t>
         </is>
       </c>
     </row>
@@ -1382,39 +1607,45 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Produtos</t>
+          <t>Modo de uso</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Como o cliente pode conferir se um cosmético é regular no Brasil?</t>
+          <t>Qual é o protocolo correto de pausa e enxágue da Não Chore Mais?</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Pelo registro ou notificação na Anvisa informado no rótulo</t>
+          <t>Pausa de 10 minutos e enxágue de 70% do produto</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Se a embalagem estiver bonita e lacrada</t>
+          <t>Pausa de 40 a 70 minutos e enxágue de 100% do produto, só com água</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>A Anvisa exige regularização para cosméticos. O número no rótulo pode ser consultado no site do órgão.</t>
+          <t>10 min e 70% de enxágue é o protocolo do CauterGloss, não da progressiva.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Embalagem não garante procedência nem segurança. Produtos irregulares podem ter formulação inadequada.</t>
-        </is>
-      </c>
+          <t>Menos tempo em cabelo danificado e mais em cabelo virgem, grosso ou afro. É essencial remover todo o produto antes de secar e passar a prancha (10 a 20 vezes em mechas finas).</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>nao-chore-mais</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1422,39 +1653,45 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Cuidados e avisos</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Qual a melhor escolha para cabelos finos e que ficam pesados facilmente?</t>
+          <t>O que fazer durante a pausa da Não Chore Mais?</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Cremes densos e ricos em óleos</t>
+          <t>Não massagear o produto no couro cabeludo nem usar touca ou plástico</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Texturas leves, como sprays e séruns, em pequena quantidade</t>
+          <t>Cobrir com touca plástica para o produto agir melhor</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Formulações muito densas deixam o cabelo achatado e oleoso mais rápido.</t>
+          <t>A aplicação evita o couro cabeludo, e a touca ou a massagem não são indicadas na pausa. Também se evita expor a cabeça ao sol.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Fios finos têm menos massa e são mais afetados por peso. Leves ajudam a hidratar sem perder volume.</t>
-        </is>
-      </c>
+          <t>Touca ou plástico na pausa não é indicado pelo protocolo da progressiva.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>nao-chore-mais</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1462,22 +1699,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Cabelo</t>
+          <t>Qual usar?</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Como cuidar do cabelo depois de praia ou piscina?</t>
+          <t>Depois da progressiva, o que usar nas 3 primeiras lavagens?</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Enxaguar com água limpa logo após e hidratar</t>
+          <t>NeutraQuimic</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Deixar secar com sal e cloro, pois protegem o fio</t>
+          <t>Shampoo Anti Resíduo</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1487,21 +1724,1816 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Sal e cloro ressecam e podem alterar a cor. Enxaguar remove o excesso e a hidratação repõe o que foi perdido.</t>
+          <t>O NeutraQuimic equilibra o pH e religa as pontes de dissulfeto, o que ajuda a prolongar o liso.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Sal e cloro não protegem, eles retiram água e óleo do fio, deixando-o quebradiço.</t>
-        </is>
-      </c>
+          <t>O Anti Resíduo é para antes das químicas, para limpar o fio.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>nao-chore-mais|neutraquimic|shampoo-anti-residuo</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Quando usar o Shampoo Anti Resíduo?</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Antes de procedimentos químicos, como progressiva e selagem</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Todos os dias, como shampoo de manutenção</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Ele limpa profundamente e prepara os fios. A orientação é usá-lo antes das químicas, não diariamente.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Para uso diário pós-química a marca tem a linha Day Use.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>shampoo-anti-residuo</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>O que é e para que serve</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>O que diferencia a Perfecta de outros alisantes da linha?</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>É de passo único e o creme é claro, sem pigmento matizador</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Tem dois passos e pigmento matizador</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>A Perfecta é aplicada em um só passo, sem pigmento matizador, com 12 óleos e ácido hialurônico aumentado.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Esse não é o perfil da Perfecta: ela é de passo único e sem pigmento.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>perfecta</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Com que frequência aplicar CauterGloss para manter o brilho de um alisamento da Borabella?</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>A cada 6 meses</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>A cada 20 dias</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>6 meses é espaço demais para manter o selamento cuticular.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>O CauterGloss a cada 20 dias revitaliza brilho e maciez e prolonga o selamento. Pode ser usado sempre que necessário, pois não tem ativos agressivos.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>cautergloss|perfecta</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Cuidados e avisos</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Em qual cabelo a Selagem 3D NÃO deve ser usada?</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Tons 9 ou mais, loiros claríssimos ou brancos</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Cabelos cacheados</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>A marca avisa para não usar em tons iguais ou acima de 9, e para fazer teste de mecha em cabelos fracos, finos ou descoloridos.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>A Selagem 3D é indicada também para cacheados, ondulados e coloridos (tom até 8).</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>selagem-3d</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Benefícios</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Qual é a duração do resultado da Selagem 3D?</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Até 4 meses</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Até 3 meses</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Até 4 meses é a duração anunciada da progressiva Não Chore Mais.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>A Selagem tem resultado por até 3 meses, sem ardência e compatível com outras marcas.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>selagem-3d|nao-chore-mais</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>O que é e para que serve</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Qual afirmação sobre o Boratx está correta?</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Contém formol em baixa concentração</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Não contém formol nem ácido glioxílico e tem 19 aminoácidos</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Toda a linha Borabella é livre de formol.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>O Boratx é livre de formol e ácido glioxílico, com BioComplex (aminoácidos, ácidos aspártico e glutâmico, hialurônico e proteína da seda).</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>boratx</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Cuidados e avisos</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Antes de aplicar o Boratx, o que a marca recomenda?</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Fazer teste de mecha</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Aplicar direto, sem teste, pois é compatível com tudo</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Ele é compatível com químicas anteriores, mas o teste de mecha é recomendado.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Compatibilidade não dispensa o teste de mecha.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>boratx</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>O que é e para que serve</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>O que significa o Perfeitox ser 'termoativado'?</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Só funciona em cabelo seco ao natural, sem calor</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>A fórmula é potencializada pelo calor do secador e da prancha</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>É o contrário: o calor ajuda a ativar o tratamento.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>A ação termoativada dá resultados mais rápidos e visíveis com secadores e pranchas.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>perfeitox</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Benefícios</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Qual ativo do Perfeitox sela as cutículas e dá brilho gloss?</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Extrato de tamarindo</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Óleo de rícino</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>O extrato de tamarindo confere brilho gloss e sela as cutículas no Perfeitox.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>O óleo de rícino aparece no Brush, não é o ativo de brilho do Perfeitox.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>perfeitox|brush</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Qual é o tempo de pausa do NeutraQuimic?</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10 a 15 minutos</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>40 a 70 minutos</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Após a química, aplique no cabelo úmido da raiz às pontas, enluvando e massageando o couro, por 10 a 15 min.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>40 a 70 min é a pausa da progressiva Não Chore Mais.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>neutraquimic</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Qual usar?</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>A cliente reclama de mau cheiro quando o cabelo molha após progressiva ácida. Qual produto?</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>NeutraQuimic</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>CauterGloss</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>O cheiro vem da liberação de enxofre; o NeutraQuimic neutraliza e elimina o mau cheiro quando molhado.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>O CauterGloss sela e dá brilho, mas a função de eliminar o cheiro é do NeutraQuimic.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>neutraquimic|cautergloss</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Cuidados e avisos</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>O CauterGloss pode ser usado em gestantes, lactantes e crianças?</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Não, é só para adultos</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Sim, é livre de ativos agressivos e tem pH 4,5</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>O CauterGloss é liberado, inclusive para crianças.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>A marca libera o uso, pois ele não tem aldeídos, ácidos ou químicas agressivas.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>cautergloss</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Qual usar?</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Cabelo reto, poroso e fragilizado que não pode mais receber química. O que indicar?</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>CauterGloss</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Uma nova progressiva</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>O CauterGloss entrega antifrizz, brilho e reparação sem nova química.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Mais química em fio fragilizado pode causar mais dano.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>cautergloss</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Como finalizar a aplicação do CauterGloss?</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Deixar 10 min e enxaguar 70% do produto</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Deixar 40 min e enxaguar 100%</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>O cabelo úmido recebe o produto e, após 10 min, enxágua-se 70%. Depois escova-se (prancha de 4 a 6 vezes, máx. 190 °C) ou seca-se ao natural, se cacheado.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Esse é o protocolo da progressiva, não do CauterGloss.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>cautergloss|nao-chore-mais</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Como usar o SOS Extreme?</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>40 minutos e enxágue com shampoo</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Da raiz às pontas, 5 minutos, enxágue só com água</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Esse tempo não é o do SOS, que age em apenas 5 minutos.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Aplicação rápida: enluvar e massagear, 5 min, enxaguar apenas com água.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>sos-extreme</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Qual usar?</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Cabelo elástico, emborrachado e que quebra na escova. O que indicar?</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>SOS Extreme</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Selagem 3D</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>O SOS Extreme é anti-quebra e anti-emborrachamento, facilitando o desembaraço, e é compatível com todas as químicas.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>A selagem seria nova química, o oposto do que o fio precisa.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>sos-extreme|selagem-3d</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Como funciona o cronograma do Pra Tudo?</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>6 aplicações com intervalo de 4 dias</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>1 aplicação por mês</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Para repor massa, hidratar, nutrir e reparar, a marca indica 6 aplicações a cada 4 dias.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Uma por mês é pouco para o cronograma.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>pra-tudo</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Benefícios</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Qual é o diferencial da máscara Pra Tudo?</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Só hidrata e exige condicionador</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Hidrata, nutre e reconstrói com um único produto, com mais de 25 ativos</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>O Pra Tudo une hidratação, nutrição e reconstrução em um passo.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>São mais de 25 ativos, incluindo nanoqueratina, colágeno, proteína da seda e 16 aminoácidos.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>pra-tudo</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Como aplicar a máscara Pra Tudo?</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Enxaguar imediatamente</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Deixar 5 a 10 min e enxaguar 80%</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Enxaguar na hora não deixa o tratamento agir.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Aplique da raiz às pontas, mecha a mecha, deixe 5 a 10 min e enxágue 80%. Ela também pode ser ativada com escova.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>pra-tudo</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Cuidados e avisos</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Quem pode usar o Day Use Pós-Química?</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Gestantes e lactantes, em qualquer cabelo e química</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Apenas cabelos virgens</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Ele é liberado para gestantes e lactantes e compatível com todos os cabelos e químicas.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Ele foi feito justamente para cabelos que passaram por química.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>day-use-pos-quimica</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>O que é e para que serve</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Quantos passos tem o kit Day Use Pós-Química?</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>3 (shampoo, condicionador e máscara)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>2 (shampoo e máscara)</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Shampoo, condicionador e máscara são as linhas Day Use Super.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>O kit é composto por shampoo e máscara; a máscara fica de 5 a 7 min.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>day-use-pos-quimica</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Qual usar?</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Cabelo poroso, opaco e com frizz. Qual linha Day Use indicar?</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Super Reparação</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Super Nutrição</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>A Reparação foca em quebra e fios quimicamente tratados.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>A Super Nutrição traz óleos como macadâmia, coco e babaçu para nutrir e controlar o frizz.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>day-use-nutricao|day-use-reparacao</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Qual usar?</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Qual linha Day Use traz pantenol e ácido hialurônico para ressecados e opacos?</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Super Nutrição</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Super Hidratação</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>A Nutrição usa óleos preciosos e vitaminas A e E.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Esses ativos hidratam e protegem contra ressecamento.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>day-use-hidratacao|day-use-nutricao</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Qual usar?</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Fios frágeis e quebradiços por química. Qual linha Day Use?</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Super Hidratação</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Super Reparação</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>A Hidratação trabalha ressecamento, não quebra.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Queratina hidrolisada, proteína da seda e da soja fortalecem a fibra.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>day-use-reparacao|day-use-hidratacao</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Nas linhas Day Use Super, qual é o tempo correto de condicionador e máscara?</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Condicionador 3 a 5 min; máscara 5 a 7 min</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Condicionador 10 min; máscara 1 min</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>O condicionador é desembaraçado com os dedos antes do enxágue; a máscara é enluvada.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Esse tempo não segue o protocolo.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>day-use-hidratacao</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Qual é a ordem de uso do kit Scalp Repair?</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Fluido, depois enxágue e shampoo</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Shampoo, condicionador e depois fluido sem enxágue</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>O fluido é a última etapa.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Shampoo: 3 min e ao menos 2 aplicações. Condicionador: 3 min. O fluido vai no couro cabeludo e não se enxágua.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>scalp-repair</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>O que é e para que serve</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Por que o couro cabeludo pode irritar e cair após a química?</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>O pH natural é cerca de 5 e as químicas operam em pH 2 ou até 11</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Porque o cabelo estava sujo</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Esse desequilíbrio altera a microbiota e pode causar coceira, vermelhidão e queda. O Scalp Repair restaura o pH.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>A causa é o desequilíbrio de pH.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>scalp-repair</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Como aplicar o Leave-in Volumize?</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>No cabelo úmido, do meio às pontas, sem enxaguar</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Na raiz com cabelo seco, depois enxaguar</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Pequena quantidade, distribuída com as mãos ou pente; seca ao natural ou com secador.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Ele é um leave-in, sem enxágue, e vai do meio às pontas.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>volumize</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Qual usar?</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Cabelo fino e afinado por químicas. O que indicar para dar corpo?</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Elixir Light</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Leave-in Volumize</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>O Elixir Light nutre sem pesar, mas não é indicado para engrossar o fio.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>O Volumize aumenta o calibre da fibra e a densidade.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>volumize|elixir-light</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Qual usar?</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Cliente com queda e irritação do couro após descoloração. O que indicar?</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Scalp Repair</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Biokeratin</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>O Scalp Repair age no couro, restaurando o pH e fortalecendo folículos.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>A Biokeratin é spray para recuperar o fio, não trata o couro.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>scalp-repair|biokeratin</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Como usar o Elixir 12 Oils como umectação?</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Aplicar no comprimento e pontas antes de dormir</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Aplicar na raiz pela manhã</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>O óleo também serve como pré-shampoo nos fios secos e pode ser misturado à máscara.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>A umectação é no comprimento e pontas, antes de dormir.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>elixir-12-oils</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>O que é e para que serve</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Qual a diferença do Elixir Light para o Elixir 12 Oils?</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>O Light é leve, com ômegas 3, 6 e 9; o 12 Oils reúne 12 óleos nobres</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>O Light tem pigmento matizador</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Ambos são finalizadores; o Light é a opção que nutre sem pesar.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Nenhum dos dois tem pigmento.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>elixir-light|elixir-12-oils</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>O que é e para que serve</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Qual é a composição do Óleo de Argan e Macadâmia?</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Rícino, pracaxi e sericina</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Argan, macadâmia e linum</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Rícino, pracaxi e sericina fazem parte do Brush.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>São os óleos do reparador de pontas.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>oleo-argan|brush</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Benefícios</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Em quanto o Brush reduz o tempo de secagem?</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Até 70%</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Até 30%</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>70% é o índice de redução de acúmulo de danos do NeutraQuimic.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>O Brush também tem proteção térmica, da cor e UV.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>brush|neutraquimic</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Como aplicar o Brush?</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Aplicar apenas no cabelo seco</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Agitar, borrifar no cabelo úmido sem excesso de água e secar</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>O Brush é aplicado no úmido.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Depois de lavar e tirar o excesso de água, borrife no comprimento e escove ou seque ao natural.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>brush</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Quais são os usos do Shield?</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Apenas perfume</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Protetor térmico no molhado, desembaraçante a seco e perfume</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>O Shield é multifuncional.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>No molhado, borrife antes do secador ou da prancha; a seco, antes de escova ou pente; como perfume, borrife levemente.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Modo de uso</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Como usar a Biokeratin?</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Borrifar no cabelo limpo e úmido, esperar 5 min e secar sem enxaguar</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Aplicar e enxaguar após 5 min</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Depois de aguardar, seque com secador e escova e finalize como preferir.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Ela não é enxaguada.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>biokeratin</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>O que é e para que serve</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Por que a Biokeratin é 'bioidêntica'?</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>É feita de queratina animal convencional</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Foi desenvolvida por engenharia genética para imitar a queratina humana</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>A fórmula é desenvolvida em laboratório.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Por isso penetra nas camadas profundas e fortalece sem enrijecer.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>biokeratin</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Qual usar?</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Para facilitar a escova e secar mais rápido, o que usar?</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Elixir 12 Oils</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Brush 9x1</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>O Elixir 12 Oils é finalizador que nutre e dá brilho.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>O Brush facilita o deslizamento da escova e reduz até 30% o tempo de secagem.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>brush|elixir-12-oils</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"A,B"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1512,10 +3544,652 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>linha</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>resumo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>imagem_url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>nao-chore-mais</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Não Chore Mais – Progressiva Alisante (Passo 2)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Alisamento</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Progressiva alisante sem formol e sem ácido glioxílico; liso por até 4 meses.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2026/03/nao_chore_mais_transparente_06.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>shampoo-anti-residuo</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Shampoo Anti Resíduo Abre Cutículas (Passo 1)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Preparação</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza profunda antes de procedimentos químicos.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://static.dotcosmeticos.com.br/media/catalog/product/cache/1/thumbnail/450x450/040ec09b1e35df139433887a97daa66f/b/o/borabella-ncm-shampoo-antirresiduo-1l-dot_1_2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>perfecta</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Perfecta Bio Definitive 12 Oils</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Alisamento</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Alisante orgânico de passo único com 19 aminoácidos e 12 óleos; creme claro, sem pigmento matizador.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2026/03/perfecta_transparente.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>selagem-3d</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Selagem 3D Brilho Gloss Sealant</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Selagem</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Selagem semi definitiva com BioComplex; resultado por até 3 meses.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2026/03/selagem_transparente-01.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>boratx</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Boratx 19 Amino (Bt-o.x)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Botox capilar</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Alinha, hidrata e repõe massa; sem formol e sem ácido glioxílico.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2026/05/home_boratx_2026-01.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>perfeitox</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Perfeitox Bio Definitive System 12 Oils</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Alinhamento</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Tratamento termoativado de alinhamento e nutrição com 19 aminoácidos e 12 óleos.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2026/07/perfeitox_2026_001.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>neutraquimic</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>NeutraQuimic</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Pós-química</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Neutraliza o pH, religa pontes de dissulfeto e elimina o cheiro após a química.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2026/03/Neutraquimic-26-002.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>cautergloss</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CauterGloss – Espelhamento e Blindagem Cuticular</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Cauterização</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Cauterização pH 4,5 que sela cutículas; liberada para gestantes, lactantes e crianças.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2026/03/Cauter-Gloss-a-650.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>sos-extreme</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SOS Extreme – Reconstrutor Anti-Emborrachamento</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Reconstrução</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Reconstrutor de ação rápida (5 min) para cabelos muito danificados ou emborrachados.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2025/12/sos_3d_transparente-2025-1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>pra-tudo</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Pra Tudo 25 Ativos – Cronograma Capilar Único</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Shampoo + máscara que hidrata, nutre e reconstrói com um único produto.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2025/11/3D_fundo_transparente.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>day-use-pos-quimica</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Day Use Kit Pós-Química</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Home care</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Kit diário (shampoo + máscara) que prolonga o resultado das químicas.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2024/08/produto_dayuse_24.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>day-use-nutricao</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Day Use Super Nutrição</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Home care</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Shampoo, condicionador e máscara com óleos preciosos para nutrir e controlar o frizz.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2025/03/day_use_nutricao1080.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>day-use-hidratacao</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Day Use Super Hidratação</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Home care</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Shampoo, condicionador e máscara com pantenol e ácido hialurônico para hidratar.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2025/03/day_use_hidratacao1080.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>day-use-reparacao</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Day Use Super Reparação</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Home care</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Shampoo, condicionador e máscara com queratina e proteínas para fortalecer.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2025/03/day_use_reparacao1080.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>scalp-repair</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Scalp Repair (kit 3 etapas)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Couro cabeludo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Shampoo, condicionador e fluido que tratam queda, quebra e irritação pós-química.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2025/03/scalp-repair.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>volumize</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Leave-in Volumize</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Fios finos</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Leave-in que engrossa e dá corpo a fios finos e afinados.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2026/05/volumize_borabella.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>elixir-12-oils</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Elixir 12 Oils</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Finalizador</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Óleo finalizador e protetor com 12 óleos nobres.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2026/08/elixir-12oils-2026.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>elixir-light</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Elixir Light</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Finalizador</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Óleo leve com ômegas 3, 6 e 9 que nutre sem pesar.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2024/10/Borabella_Elixir_Light.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>oleo-argan</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Óleo de Argan e Macadâmia</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Finalizador</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Reparador de pontas com argan, macadâmia e linum.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2026/08/argan_oil2x-2026.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>brush</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Fluído de Escova Brush 9x1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Finalizador</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Fluído termoativado 9 em 1 que facilita a escova e reduz até 30% o tempo de secagem.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2026/05/brush_transparente_2026-1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Shield – Perfume e Protetor Térmico</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Finalizador</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Spray que une protetor térmico, desembaraçante e perfume capilar.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2025/02/shield_3d_2025.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>biokeratin</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Biokeratin – Queratina Líquida Bioidêntica</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Queratina líquida em spray que repara sem enrijecer.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borabella.com.br/wp-content/uploads/2025/03/Biokeratin-240ML-nova.png</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1526,44 +4200,51 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>1. Na aba 'perguntas', preencha uma nova linha no fim da tabela (a linha 2 é um exemplo de formato).</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1. Na aba 'perguntas', preencha uma nova linha no fim da tabela. id: número sequencial.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2. id: número sequencial. categoria: agrupa o tema (ex.: Cabelo, Produtos, Atendimento).</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2. categoria: agrupa o tema. Use exatamente 'Reconheça a embalagem' para as perguntas visuais (aparecem no modo 'Reconhecer embalagens').</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>3. opcao_a e opcao_b: os dois cards. correta: A ou B (só uma resposta correta).</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3. correta: A ou B. Só uma resposta certa por pergunta; o site embaralha a posição dos cards.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>4. explicacao_a e explicacao_b: o texto que aparece no verso de cada card. Explique o porquê, também na errada.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4. produtos: slug(s) da aba 'produtos' mostrados DEPOIS da resposta (separe vários com |). Obrigatório.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>5. Salve e rode: python tools/xlsx_para_csv.py</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5. imagem_pergunta: preencha com um slug só nas perguntas visuais. Nessas, a imagem aparece ANTES da resposta, então as opções devem descrever funções, nunca citar o nome do produto.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>6. Recarregue o site. Pronto.</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6. Para um produto novo, adicione uma linha na aba 'produtos' (slug, nome, linha, resumo, imagem_url) e rode tools/baixar_imagens.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7. Depois, rode: python tools/xlsx_para_csv.py</t>
         </is>
       </c>
     </row>
